--- a/artfynd/A 54269-2025 artfynd.xlsx
+++ b/artfynd/A 54269-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16817797</v>
+        <v>16817789</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548456.6032817457</v>
+        <v>548077</v>
       </c>
       <c r="R2" t="n">
-        <v>7130789.354847561</v>
+        <v>7130788</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16817794</v>
+        <v>16817788</v>
       </c>
       <c r="B3" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548358.9952213872</v>
+        <v>548054</v>
       </c>
       <c r="R3" t="n">
-        <v>7130776.095808296</v>
+        <v>7130785</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16817796</v>
+        <v>16817793</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548424.3926568511</v>
+        <v>548251</v>
       </c>
       <c r="R4" t="n">
-        <v>7130791.886986161</v>
+        <v>7130772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16817787</v>
+        <v>16817795</v>
       </c>
       <c r="B5" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548070.6426864724</v>
+        <v>548382</v>
       </c>
       <c r="R5" t="n">
-        <v>7130783.733900023</v>
+        <v>7130790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16817790</v>
+        <v>16817787</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548082.7038552515</v>
+        <v>548071</v>
       </c>
       <c r="R6" t="n">
-        <v>7130790.869400935</v>
+        <v>7130784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16817788</v>
+        <v>16817794</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548053.6648794308</v>
+        <v>548359</v>
       </c>
       <c r="R7" t="n">
-        <v>7130785.205410387</v>
+        <v>7130776</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1248,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16817789</v>
+        <v>16817790</v>
       </c>
       <c r="B8" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548076.6664940635</v>
+        <v>548083</v>
       </c>
       <c r="R8" t="n">
-        <v>7130787.735728722</v>
+        <v>7130791</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1349,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16817793</v>
+        <v>16817792</v>
       </c>
       <c r="B9" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548250.8121408544</v>
+        <v>548215</v>
       </c>
       <c r="R9" t="n">
-        <v>7130771.791989016</v>
+        <v>7130756</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,19 +1450,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16817791</v>
+        <v>16817796</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548124.8224065201</v>
+        <v>548424</v>
       </c>
       <c r="R10" t="n">
-        <v>7130794.13311622</v>
+        <v>7130792</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,19 +1551,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16817795</v>
+        <v>16817797</v>
       </c>
       <c r="B11" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548381.8123739455</v>
+        <v>548457</v>
       </c>
       <c r="R11" t="n">
-        <v>7130790.348655664</v>
+        <v>7130789</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,19 +1652,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16817792</v>
+        <v>16817791</v>
       </c>
       <c r="B12" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548214.9823720281</v>
+        <v>548125</v>
       </c>
       <c r="R12" t="n">
-        <v>7130755.599312249</v>
+        <v>7130794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,19 +1753,9 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,122 +1779,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>16817798</v>
-      </c>
-      <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>frostberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>548475.5355836514</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7130801.810406344</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Tåsjö</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Susanne Wiik</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 54269-2025 artfynd.xlsx
+++ b/artfynd/A 54269-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817789</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817788</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817793</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817795</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817787</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817794</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817790</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817792</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817796</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817797</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,8 +1838,26 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16817791</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>